--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118847474</v>
+        <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>91867</v>
+        <v>93355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5445</v>
+        <v>2075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579164</v>
+        <v>579209</v>
       </c>
       <c r="R2" t="n">
-        <v>6398564</v>
+        <v>6398573</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På nedfallen ekgren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,13 +785,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847474</t>
+          <t>https://artportalen.se/Sighting/137104267</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118847543</v>
+        <v>118847474</v>
       </c>
       <c r="B3" t="n">
         <v>91867</v>
@@ -840,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579181</v>
+        <v>579164</v>
       </c>
       <c r="R3" t="n">
-        <v>6398551</v>
+        <v>6398564</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,13 +899,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118847543</t>
+          <t>https://artportalen.se/Sighting/118847474</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118865667</v>
+        <v>118847543</v>
       </c>
       <c r="B4" t="n">
         <v>91867</v>
@@ -938,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -954,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579220</v>
+        <v>579181</v>
       </c>
       <c r="R4" t="n">
-        <v>6398579</v>
+        <v>6398551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,13 +1013,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865667</t>
+          <t>https://artportalen.se/Sighting/118847543</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118865677</v>
+        <v>118865667</v>
       </c>
       <c r="B5" t="n">
         <v>91867</v>
@@ -1052,12 +1049,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579225</v>
+        <v>579220</v>
       </c>
       <c r="R5" t="n">
-        <v>6398552</v>
+        <v>6398579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,13 +1127,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865677</t>
+          <t>https://artportalen.se/Sighting/118865667</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118865749</v>
+        <v>118865677</v>
       </c>
       <c r="B6" t="n">
         <v>91867</v>
@@ -1166,12 +1163,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1182,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579228</v>
+        <v>579225</v>
       </c>
       <c r="R6" t="n">
-        <v>6398560</v>
+        <v>6398552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,13 +1241,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865749</t>
+          <t>https://artportalen.se/Sighting/118865677</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118865796</v>
+        <v>118865749</v>
       </c>
       <c r="B7" t="n">
         <v>91867</v>
@@ -1280,12 +1277,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1296,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579224</v>
+        <v>579228</v>
       </c>
       <c r="R7" t="n">
-        <v>6398565</v>
+        <v>6398560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,48 +1355,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865796</t>
+          <t>https://artportalen.se/Sighting/118865749</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118281573</v>
+        <v>118865796</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579230</v>
+        <v>579224</v>
       </c>
       <c r="R8" t="n">
-        <v>6398644</v>
+        <v>6398565</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1451,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1468,59 +1469,62 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118281573</t>
+          <t>https://artportalen.se/Sighting/118865796</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118865652</v>
+        <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27067, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579059</v>
+        <v>579355</v>
       </c>
       <c r="R9" t="n">
-        <v>6398651</v>
+        <v>6398671</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,25 +1551,21 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1583,13 +1583,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865652</t>
+          <t>https://artportalen.se/Sighting/137103934</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118865715</v>
+        <v>118281573</v>
       </c>
       <c r="B10" t="n">
         <v>57950</v>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579432</v>
+        <v>579230</v>
       </c>
       <c r="R10" t="n">
-        <v>6398712</v>
+        <v>6398644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,17 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,33 +1693,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865715</t>
+          <t>https://artportalen.se/Sighting/118281573</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119180160</v>
+        <v>118865652</v>
       </c>
       <c r="B11" t="n">
-        <v>58067</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100090</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1732,16 +1727,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1751,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579278</v>
+        <v>579059</v>
       </c>
       <c r="R11" t="n">
-        <v>6398844</v>
+        <v>6398651</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,12 +1772,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,22 +1802,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119180160</t>
+          <t>https://artportalen.se/Sighting/118865652</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131740413</v>
+        <v>118865715</v>
       </c>
       <c r="B12" t="n">
-        <v>4989</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,34 +1825,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100307</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ugglekärr Nordost, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579462</v>
+        <v>579432</v>
       </c>
       <c r="R12" t="n">
-        <v>6398836</v>
+        <v>6398712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,12 +1887,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,81 +1912,73 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740413</t>
+          <t>https://artportalen.se/Sighting/118865715</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118865729</v>
+        <v>137103912</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27067, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579436</v>
+        <v>579379</v>
       </c>
       <c r="R13" t="n">
-        <v>6398702</v>
+        <v>6398711</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,12 +2002,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,16 +2033,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865729</t>
+          <t>https://artportalen.se/Sighting/137103912</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624097</v>
+        <v>119180160</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>58067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100090</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2085,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579120</v>
+        <v>579278</v>
       </c>
       <c r="R14" t="n">
-        <v>6398550</v>
+        <v>6398844</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2115,12 +2116,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,44 +2141,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624097</t>
+          <t>https://artportalen.se/Sighting/119180160</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740065</v>
+        <v>131740413</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>4989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,7 +2191,7 @@
         <v>579462</v>
       </c>
       <c r="R15" t="n">
-        <v>6398659</v>
+        <v>6398836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,12 +2218,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,17 +2243,575 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740413</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118865729</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579436</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398702</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118865729</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119624097</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 27067, Stormbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579120</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398550</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624097</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131740065</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ugglekärr Nordost, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579462</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6398659</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
           <t>Lynx Beverskog</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131740065</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137103974</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 27067, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579318</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103974</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137103991</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 27067, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579318</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103991</t>
         </is>
       </c>
     </row>
@@ -2272,6 +2831,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93355</v>
+        <v>93361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93361</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2039,27 +2039,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119180160</v>
+        <v>137220883</v>
       </c>
       <c r="B14" t="n">
-        <v>58067</v>
+        <v>58005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100090</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2076,20 +2076,20 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27067, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579278</v>
+        <v>579283</v>
       </c>
       <c r="R14" t="n">
-        <v>6398844</v>
+        <v>6398555</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2141,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119180160</t>
+          <t>https://artportalen.se/Sighting/137220883</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131740413</v>
+        <v>137220894</v>
       </c>
       <c r="B15" t="n">
-        <v>4989</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,34 +2164,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100307</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ugglekärr Nordost, Sm</t>
+          <t>A 27067, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579462</v>
+        <v>579311</v>
       </c>
       <c r="R15" t="n">
-        <v>6398836</v>
+        <v>6398586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,12 +2226,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,81 +2251,73 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740413</t>
+          <t>https://artportalen.se/Sighting/137220894</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118865729</v>
+        <v>137220899</v>
       </c>
       <c r="B16" t="n">
-        <v>58114</v>
+        <v>58005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27067, Atormandebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579436</v>
+        <v>579323</v>
       </c>
       <c r="R16" t="n">
-        <v>6398702</v>
+        <v>6398685</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,12 +2341,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,16 +2377,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865729</t>
+          <t>https://artportalen.se/Sighting/137220899</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119624097</v>
+        <v>119180160</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>58067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2384,21 +2394,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100090</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2420,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579120</v>
+        <v>579278</v>
       </c>
       <c r="R17" t="n">
-        <v>6398550</v>
+        <v>6398844</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,12 +2460,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,44 +2485,44 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624097</t>
+          <t>https://artportalen.se/Sighting/119180160</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131740065</v>
+        <v>131740413</v>
       </c>
       <c r="B18" t="n">
-        <v>58136</v>
+        <v>4989</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,7 +2535,7 @@
         <v>579462</v>
       </c>
       <c r="R18" t="n">
-        <v>6398659</v>
+        <v>6398836</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,12 +2562,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,7 +2587,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2587,16 +2597,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740065</t>
+          <t>https://artportalen.se/Sighting/131740413</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137103974</v>
+        <v>118865729</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,7 +2633,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2636,14 +2646,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27067, Stormandebo, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579318</v>
+        <v>579436</v>
       </c>
       <c r="R19" t="n">
-        <v>6398644</v>
+        <v>6398702</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2670,12 +2680,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,59 +2711,63 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137103974</t>
+          <t>https://artportalen.se/Sighting/118865729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137103991</v>
+        <v>119624097</v>
       </c>
       <c r="B20" t="n">
-        <v>58164</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 27067, Stormandebo, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579318</v>
+        <v>579120</v>
       </c>
       <c r="R20" t="n">
-        <v>6398644</v>
+        <v>6398550</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,12 +2794,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,6 +2824,336 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624097</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131740065</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ugglekärr Nordost, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579462</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6398659</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740065</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137103974</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 27067, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579318</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103974</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137103991</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 27067, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579318</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137103991</t>
         </is>
@@ -2836,6 +3180,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93367</v>
+        <v>93380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>137103912</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137220883</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>137220894</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137220899</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137103974</v>
       </c>
       <c r="B22" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137103991</v>
       </c>
       <c r="B23" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93380</v>
+        <v>93382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>137103912</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137220883</v>
       </c>
       <c r="B14" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>137220894</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137220899</v>
       </c>
       <c r="B16" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137103974</v>
       </c>
       <c r="B22" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>137103991</v>
       </c>
       <c r="B23" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,27 +1589,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118281573</v>
+        <v>137269034</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>58036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1617,28 +1617,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27737, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579230</v>
+        <v>579204</v>
       </c>
       <c r="R10" t="n">
-        <v>6398644</v>
+        <v>6398534</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,13 +1693,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118281573</t>
+          <t>https://artportalen.se/Sighting/137269034</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118865652</v>
+        <v>118281573</v>
       </c>
       <c r="B11" t="n">
         <v>57950</v>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579059</v>
+        <v>579230</v>
       </c>
       <c r="R11" t="n">
-        <v>6398651</v>
+        <v>6398644</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,17 +1772,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,13 +1803,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865652</t>
+          <t>https://artportalen.se/Sighting/118281573</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118865715</v>
+        <v>118865652</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579432</v>
+        <v>579059</v>
       </c>
       <c r="R12" t="n">
-        <v>6398712</v>
+        <v>6398651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,16 +1918,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865715</t>
+          <t>https://artportalen.se/Sighting/118865652</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137103912</v>
+        <v>118865715</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,14 +1963,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 27067, Stormandebo, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579379</v>
+        <v>579432</v>
       </c>
       <c r="R13" t="n">
-        <v>6398711</v>
+        <v>6398712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,12 +1997,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,13 +2033,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137103912</t>
+          <t>https://artportalen.se/Sighting/118865715</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137220883</v>
+        <v>137103912</v>
       </c>
       <c r="B14" t="n">
         <v>58020</v>
@@ -2067,18 +2067,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,13 +2078,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579283</v>
+        <v>579379</v>
       </c>
       <c r="R14" t="n">
-        <v>6398555</v>
+        <v>6398711</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,12 +2108,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,13 +2139,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220883</t>
+          <t>https://artportalen.se/Sighting/137103912</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137220894</v>
+        <v>137220883</v>
       </c>
       <c r="B15" t="n">
         <v>58020</v>
@@ -2181,14 +2173,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2196,13 +2188,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579311</v>
+        <v>579283</v>
       </c>
       <c r="R15" t="n">
-        <v>6398586</v>
+        <v>6398555</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2232,11 +2224,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,13 +2249,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220894</t>
+          <t>https://artportalen.se/Sighting/137220883</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137220899</v>
+        <v>137220894</v>
       </c>
       <c r="B16" t="n">
         <v>58020</v>
@@ -2299,22 +2286,18 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 27067, Atormandebo, Sm</t>
+          <t>A 27067, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579323</v>
+        <v>579311</v>
       </c>
       <c r="R16" t="n">
-        <v>6398685</v>
+        <v>6398586</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,33 +2360,33 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137220899</t>
+          <t>https://artportalen.se/Sighting/137220894</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119180160</v>
+        <v>137220899</v>
       </c>
       <c r="B17" t="n">
-        <v>58067</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100090</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2411,32 +2394,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>A 27067, Atormandebo, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579278</v>
+        <v>579323</v>
       </c>
       <c r="R17" t="n">
-        <v>6398844</v>
+        <v>6398685</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,12 +2435,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,60 +2465,72 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119180160</t>
+          <t>https://artportalen.se/Sighting/137220899</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131740413</v>
+        <v>119180160</v>
       </c>
       <c r="B18" t="n">
-        <v>4989</v>
+        <v>58067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100307</v>
+        <v>100090</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ugglekärr Nordost, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579462</v>
+        <v>579278</v>
       </c>
       <c r="R18" t="n">
-        <v>6398836</v>
+        <v>6398844</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,12 +2554,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,81 +2574,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740413</t>
+          <t>https://artportalen.se/Sighting/119180160</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118865729</v>
+        <v>131740413</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>4989</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 27067, Stormbo, Sm</t>
+          <t>Ugglekärr Nordost, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579436</v>
+        <v>579462</v>
       </c>
       <c r="R19" t="n">
-        <v>6398702</v>
+        <v>6398836</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,12 +2656,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,24 +2676,28 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118865729</t>
+          <t>https://artportalen.se/Sighting/131740413</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119624097</v>
+        <v>118865729</v>
       </c>
       <c r="B20" t="n">
         <v>58114</v>
@@ -2747,7 +2727,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2764,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579120</v>
+        <v>579436</v>
       </c>
       <c r="R20" t="n">
-        <v>6398550</v>
+        <v>6398702</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2794,12 +2774,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,16 +2805,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624097</t>
+          <t>https://artportalen.se/Sighting/118865729</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131740065</v>
+        <v>119624097</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,20 +2839,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ugglekärr Nordost, Sm</t>
+          <t>A 27067, Stormbo, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579462</v>
+        <v>579120</v>
       </c>
       <c r="R21" t="n">
-        <v>6398659</v>
+        <v>6398550</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2896,12 +2888,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,31 +2908,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lynx Beverskog</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740065</t>
+          <t>https://artportalen.se/Sighting/119624097</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137103974</v>
+        <v>131740065</v>
       </c>
       <c r="B22" t="n">
-        <v>58184</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,32 +2953,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 27067, Stormandebo, Sm</t>
+          <t>Ugglekärr Nordost, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579318</v>
+        <v>579462</v>
       </c>
       <c r="R22" t="n">
-        <v>6398644</v>
+        <v>6398659</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3014,12 +2990,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,59 +3010,63 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Lynx Beverskog</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137103974</t>
+          <t>https://artportalen.se/Sighting/131740065</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137103991</v>
+        <v>137103974</v>
       </c>
       <c r="B23" t="n">
-        <v>58179</v>
+        <v>58184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3154,6 +3134,112 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103974</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137103991</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 27067, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>579318</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6398644</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137103991</t>
         </is>
@@ -3183,6 +3269,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93382</v>
+        <v>93385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93385</v>
+        <v>93395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137269034</v>
       </c>
       <c r="B10" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137103912</v>
       </c>
       <c r="B14" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137220883</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>137220894</v>
       </c>
       <c r="B16" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137220899</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>137103974</v>
       </c>
       <c r="B23" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137103991</v>
       </c>
       <c r="B24" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137269034</v>
       </c>
       <c r="B10" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137103912</v>
       </c>
       <c r="B14" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137220883</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>137220894</v>
       </c>
       <c r="B16" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137220899</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>137103974</v>
       </c>
       <c r="B23" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137103991</v>
       </c>
       <c r="B24" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137269034</v>
       </c>
       <c r="B10" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137103912</v>
       </c>
       <c r="B14" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137220883</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>137220894</v>
       </c>
       <c r="B16" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137220899</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>137103974</v>
       </c>
       <c r="B23" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137103991</v>
       </c>
       <c r="B24" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27067-2024 artfynd.xlsx
+++ b/artfynd/A 27067-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137104267</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137103934</v>
       </c>
       <c r="B9" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>137269034</v>
       </c>
       <c r="B10" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137103912</v>
       </c>
       <c r="B14" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137220883</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>137220894</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137220899</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>137103974</v>
       </c>
       <c r="B23" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>137103991</v>
       </c>
       <c r="B24" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
